--- a/server/excel/release/英雄变强.xlsx
+++ b/server/excel/release/英雄变强.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Dùng cho tướng chiêu mộ, hối đoái hối đoái vật phẩm chờ</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguyên bảo</t>
+    <t xml:space="preserve">Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">0:4</t>
